--- a/docs/program/RKA SDIT 1.xlsx
+++ b/docs/program/RKA SDIT 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Download\Laporan Program Pesantren\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Download\Tugas Akhir\Smart_Santri\smart_santri\docs\program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC828B4C-A467-4BF5-9865-6808B8DF5183}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D881FDB4-4612-4CA2-A11D-8208ED65CC18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A9C01F18-E443-476E-A180-E6813D3F3274}"/>
   </bookViews>
@@ -1598,9 +1598,6 @@
     <t>ISI</t>
   </si>
   <si>
-    <t>PROSES</t>
-  </si>
-  <si>
     <t>PENGEMBANGAN PENDIDIK DAN TENAGA KEPENDIDIKAN</t>
   </si>
   <si>
@@ -1614,6 +1611,9 @@
   </si>
   <si>
     <t>PENGEMBANGAN PENILAIAN</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN PROSES</t>
   </si>
 </sst>
 </file>
@@ -1743,9 +1743,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1754,6 +1751,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2072,7 +2072,7 @@
   <dimension ref="A1:AZ207"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="68.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="76.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="181.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>51</v>
@@ -5678,9 +5678,9 @@
     </row>
     <row r="82" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>522</v>
-      </c>
-      <c r="B82" s="11"/>
+        <v>521</v>
+      </c>
+      <c r="B82" s="14"/>
       <c r="C82" s="8" t="s">
         <v>220</v>
       </c>
@@ -5724,7 +5724,7 @@
     </row>
     <row r="83" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A83" s="10"/>
-      <c r="B83" s="11"/>
+      <c r="B83" s="14"/>
       <c r="C83" s="8" t="s">
         <v>223</v>
       </c>
@@ -5768,7 +5768,7 @@
     </row>
     <row r="84" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A84" s="10"/>
-      <c r="B84" s="11"/>
+      <c r="B84" s="14"/>
       <c r="C84" s="8" t="s">
         <v>225</v>
       </c>
@@ -5812,7 +5812,7 @@
     </row>
     <row r="85" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A85" s="10"/>
-      <c r="B85" s="11"/>
+      <c r="B85" s="14"/>
       <c r="C85" s="8" t="s">
         <v>227</v>
       </c>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="86" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A86" s="10"/>
-      <c r="B86" s="11"/>
+      <c r="B86" s="14"/>
       <c r="C86" s="8" t="s">
         <v>229</v>
       </c>
@@ -5900,7 +5900,7 @@
     </row>
     <row r="87" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A87" s="10"/>
-      <c r="B87" s="11"/>
+      <c r="B87" s="14"/>
       <c r="C87" s="8" t="s">
         <v>231</v>
       </c>
@@ -5944,7 +5944,7 @@
     </row>
     <row r="88" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A88" s="10"/>
-      <c r="B88" s="11"/>
+      <c r="B88" s="14"/>
       <c r="C88" s="8" t="s">
         <v>233</v>
       </c>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="89" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A89" s="10"/>
-      <c r="B89" s="11"/>
+      <c r="B89" s="14"/>
       <c r="C89" s="8" t="s">
         <v>235</v>
       </c>
@@ -6032,7 +6032,7 @@
     </row>
     <row r="90" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A90" s="10"/>
-      <c r="B90" s="11"/>
+      <c r="B90" s="14"/>
       <c r="C90" s="8" t="s">
         <v>237</v>
       </c>
@@ -6076,7 +6076,7 @@
     </row>
     <row r="91" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A91" s="10"/>
-      <c r="B91" s="11"/>
+      <c r="B91" s="14"/>
       <c r="C91" s="8" t="s">
         <v>239</v>
       </c>
@@ -6120,7 +6120,7 @@
     </row>
     <row r="92" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A92" s="10"/>
-      <c r="B92" s="11"/>
+      <c r="B92" s="14"/>
       <c r="C92" s="8" t="s">
         <v>241</v>
       </c>
@@ -6164,7 +6164,7 @@
     </row>
     <row r="93" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A93" s="10"/>
-      <c r="B93" s="11"/>
+      <c r="B93" s="14"/>
       <c r="C93" s="8" t="s">
         <v>244</v>
       </c>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="94" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A94" s="10"/>
-      <c r="B94" s="11"/>
+      <c r="B94" s="14"/>
       <c r="C94" s="8" t="s">
         <v>246</v>
       </c>
@@ -6252,7 +6252,7 @@
     </row>
     <row r="95" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A95" s="10"/>
-      <c r="B95" s="11"/>
+      <c r="B95" s="14"/>
       <c r="C95" s="8" t="s">
         <v>248</v>
       </c>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="96" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A96" s="10"/>
-      <c r="B96" s="11"/>
+      <c r="B96" s="14"/>
       <c r="C96" s="8" t="s">
         <v>250</v>
       </c>
@@ -6340,7 +6340,7 @@
     </row>
     <row r="97" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B97" s="9" t="s">
         <v>253</v>
@@ -8372,7 +8372,7 @@
     </row>
     <row r="143" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B143" s="9" t="s">
         <v>362</v>
@@ -9535,8 +9535,8 @@
       <c r="AZ168" s="2"/>
     </row>
     <row r="169" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A169" s="12" t="s">
-        <v>525</v>
+      <c r="A169" s="11" t="s">
+        <v>524</v>
       </c>
       <c r="B169" s="9" t="s">
         <v>433</v>
@@ -9583,7 +9583,7 @@
       <c r="AZ169" s="2"/>
     </row>
     <row r="170" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A170" s="13"/>
+      <c r="A170" s="12"/>
       <c r="B170" s="9"/>
       <c r="C170" s="8" t="s">
         <v>437</v>
@@ -9627,7 +9627,7 @@
       <c r="AZ170" s="2"/>
     </row>
     <row r="171" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A171" s="13"/>
+      <c r="A171" s="12"/>
       <c r="B171" s="9"/>
       <c r="C171" s="8" t="s">
         <v>439</v>
@@ -9671,7 +9671,7 @@
       <c r="AZ171" s="2"/>
     </row>
     <row r="172" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A172" s="13"/>
+      <c r="A172" s="12"/>
       <c r="B172" s="9"/>
       <c r="C172" s="8" t="s">
         <v>441</v>
@@ -9715,7 +9715,7 @@
       <c r="AZ172" s="2"/>
     </row>
     <row r="173" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A173" s="13"/>
+      <c r="A173" s="12"/>
       <c r="B173" s="9"/>
       <c r="C173" s="8" t="s">
         <v>443</v>
@@ -9759,7 +9759,7 @@
       <c r="AZ173" s="2"/>
     </row>
     <row r="174" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A174" s="13"/>
+      <c r="A174" s="12"/>
       <c r="B174" s="9"/>
       <c r="C174" s="8" t="s">
         <v>445</v>
@@ -9803,7 +9803,7 @@
       <c r="AZ174" s="2"/>
     </row>
     <row r="175" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A175" s="13"/>
+      <c r="A175" s="12"/>
       <c r="B175" s="9"/>
       <c r="C175" s="8" t="s">
         <v>447</v>
@@ -9847,7 +9847,7 @@
       <c r="AZ175" s="2"/>
     </row>
     <row r="176" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A176" s="13"/>
+      <c r="A176" s="12"/>
       <c r="B176" s="9" t="s">
         <v>449</v>
       </c>
@@ -9893,7 +9893,7 @@
       <c r="AZ176" s="2"/>
     </row>
     <row r="177" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A177" s="13"/>
+      <c r="A177" s="12"/>
       <c r="B177" s="9"/>
       <c r="C177" s="8" t="s">
         <v>453</v>
@@ -9937,7 +9937,7 @@
       <c r="AZ177" s="2"/>
     </row>
     <row r="178" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A178" s="13"/>
+      <c r="A178" s="12"/>
       <c r="B178" s="9"/>
       <c r="C178" s="8" t="s">
         <v>455</v>
@@ -9981,7 +9981,7 @@
       <c r="AZ178" s="2"/>
     </row>
     <row r="179" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A179" s="13"/>
+      <c r="A179" s="12"/>
       <c r="B179" s="9"/>
       <c r="C179" s="8" t="s">
         <v>456</v>
@@ -10025,7 +10025,7 @@
       <c r="AZ179" s="2"/>
     </row>
     <row r="180" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A180" s="13"/>
+      <c r="A180" s="12"/>
       <c r="B180" s="9"/>
       <c r="C180" s="8" t="s">
         <v>458</v>
@@ -10069,7 +10069,7 @@
       <c r="AZ180" s="2"/>
     </row>
     <row r="181" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A181" s="13"/>
+      <c r="A181" s="12"/>
       <c r="B181" s="9" t="s">
         <v>460</v>
       </c>
@@ -10115,7 +10115,7 @@
       <c r="AZ181" s="2"/>
     </row>
     <row r="182" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A182" s="13"/>
+      <c r="A182" s="12"/>
       <c r="B182" s="9"/>
       <c r="C182" s="8" t="s">
         <v>463</v>
@@ -10159,7 +10159,7 @@
       <c r="AZ182" s="2"/>
     </row>
     <row r="183" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A183" s="13"/>
+      <c r="A183" s="12"/>
       <c r="B183" s="9"/>
       <c r="C183" s="8" t="s">
         <v>465</v>
@@ -10203,7 +10203,7 @@
       <c r="AZ183" s="2"/>
     </row>
     <row r="184" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A184" s="13"/>
+      <c r="A184" s="12"/>
       <c r="B184" s="9"/>
       <c r="C184" s="8" t="s">
         <v>467</v>
@@ -10247,7 +10247,7 @@
       <c r="AZ184" s="2"/>
     </row>
     <row r="185" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A185" s="13"/>
+      <c r="A185" s="12"/>
       <c r="B185" s="9"/>
       <c r="C185" s="8" t="s">
         <v>469</v>
@@ -10291,7 +10291,7 @@
       <c r="AZ185" s="2"/>
     </row>
     <row r="186" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A186" s="13"/>
+      <c r="A186" s="12"/>
       <c r="B186" s="8" t="s">
         <v>471</v>
       </c>
@@ -10337,7 +10337,7 @@
       <c r="AZ186" s="2"/>
     </row>
     <row r="187" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A187" s="13"/>
+      <c r="A187" s="12"/>
       <c r="B187" s="9" t="s">
         <v>475</v>
       </c>
@@ -10383,7 +10383,7 @@
       <c r="AZ187" s="2"/>
     </row>
     <row r="188" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A188" s="13"/>
+      <c r="A188" s="12"/>
       <c r="B188" s="9"/>
       <c r="C188" s="8" t="s">
         <v>478</v>
@@ -10427,7 +10427,7 @@
       <c r="AZ188" s="2"/>
     </row>
     <row r="189" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A189" s="14"/>
+      <c r="A189" s="13"/>
       <c r="B189" s="9"/>
       <c r="C189" s="8" t="s">
         <v>480</v>
@@ -10472,7 +10472,7 @@
     </row>
     <row r="190" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B190" s="9" t="s">
         <v>482</v>
